--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/deliverySuggestionEntity.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/deliverySuggestionEntity.xlsx
@@ -27,7 +27,43 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+  <si>
+    <t>平台</t>
+  </si>
+  <si>
+    <t>店铺</t>
+  </si>
+  <si>
+    <t>国家</t>
+  </si>
+  <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>品名</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>系统建议值</t>
+  </si>
+  <si>
+    <t>计划修正值</t>
+  </si>
+  <si>
+    <t>运营确认值</t>
+  </si>
+  <si>
+    <t>是否下推</t>
+  </si>
+  <si>
+    <t>发货备货数</t>
+  </si>
   <si>
     <t>发货计划单号</t>
   </si>
@@ -56,6 +92,9 @@
     <t>预计物流成本（系统）</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>创建方式</t>
   </si>
   <si>
@@ -71,9 +110,45 @@
     <t>更新时间</t>
   </si>
   <si>
+    <t>{.platformName}</t>
+  </si>
+  <si>
+    <t>{.shopName}</t>
+  </si>
+  <si>
+    <t>{.countryName}</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.statusName}</t>
+  </si>
+  <si>
+    <t>{.suggestDeliveryQty}</t>
+  </si>
+  <si>
+    <t>{.planDeliveryQty}</t>
+  </si>
+  <si>
+    <t>{.actualDeliveryQty}</t>
+  </si>
+  <si>
+    <t>{.isPushName}</t>
+  </si>
+  <si>
+    <t>{.deliveryStockUpQty}</t>
+  </si>
+  <si>
+    <t>{.deliveryPlanCode}</t>
+  </si>
+  <si>
     <t>{.logisticsMethodName}</t>
   </si>
   <si>
@@ -96,6 +171,9 @@
   </si>
   <si>
     <t>{.sysLogisticsCost}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
   </si>
   <si>
     <t>{.createTypeName}</t>
@@ -1041,26 +1119,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="15.625" customWidth="1"/>
-    <col min="2" max="2" width="16.125" customWidth="1"/>
-    <col min="3" max="3" width="19.5" customWidth="1"/>
-    <col min="4" max="4" width="17.625" customWidth="1"/>
-    <col min="5" max="5" width="20.875" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="21.5" customWidth="1"/>
-    <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="19.875" customWidth="1"/>
+    <col min="1" max="1" width="14.125" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="13.75" customWidth="1"/>
+    <col min="4" max="4" width="14.75" customWidth="1"/>
+    <col min="5" max="6" width="14.125" customWidth="1"/>
+    <col min="7" max="7" width="14.375" customWidth="1"/>
+    <col min="8" max="8" width="17.375" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="17.25" customWidth="1"/>
-    <col min="11" max="11" width="15.875" customWidth="1"/>
-    <col min="12" max="12" width="16.875" customWidth="1"/>
-    <col min="13" max="13" width="14.75" customWidth="1"/>
-    <col min="14" max="14" width="17.375" customWidth="1"/>
+    <col min="11" max="11" width="20.75" customWidth="1"/>
+    <col min="12" max="12" width="23.75" customWidth="1"/>
+    <col min="13" max="13" width="19.5" customWidth="1"/>
+    <col min="14" max="14" width="16.125" customWidth="1"/>
+    <col min="15" max="15" width="19.5" customWidth="1"/>
+    <col min="16" max="16" width="17.625" customWidth="1"/>
+    <col min="17" max="17" width="20.875" customWidth="1"/>
+    <col min="18" max="18" width="17" customWidth="1"/>
+    <col min="19" max="19" width="21.5" customWidth="1"/>
+    <col min="20" max="20" width="17" customWidth="1"/>
+    <col min="21" max="21" width="19.875" customWidth="1"/>
+    <col min="22" max="22" width="17.375" customWidth="1"/>
+    <col min="23" max="23" width="17.25" customWidth="1"/>
+    <col min="24" max="24" width="15.875" customWidth="1"/>
+    <col min="25" max="25" width="16.875" customWidth="1"/>
+    <col min="26" max="26" width="14.75" customWidth="1"/>
+    <col min="27" max="27" width="17.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1103,49 +1193,127 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>40</v>
+      </c>
+      <c r="O2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S2" t="s">
+        <v>45</v>
+      </c>
+      <c r="T2" t="s">
+        <v>46</v>
+      </c>
+      <c r="U2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/deliverySuggestionEntity.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/deliverySuggestionEntity.xlsx
@@ -176,7 +176,7 @@
     <t>{.remark}</t>
   </si>
   <si>
-    <t>{.createTypeName}</t>
+    <t>{.dataTypeName}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
